--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.9266552690624</v>
+        <v>2.91308148122264</v>
       </c>
       <c r="D2" t="n">
-        <v>18.17036202415929</v>
+        <v>2.952683828925885</v>
       </c>
       <c r="E2" t="n">
-        <v>10.07553615442021</v>
+        <v>1.637274625093284</v>
       </c>
       <c r="F2" t="n">
-        <v>12.14721084977219</v>
+        <v>1.973921763087981</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.51691809505517</v>
+        <v>4.958999190446465</v>
       </c>
       <c r="D3" t="n">
-        <v>20.18795784256574</v>
+        <v>3.280543149416932</v>
       </c>
       <c r="E3" t="n">
-        <v>10.07553615442021</v>
+        <v>1.637274625093284</v>
       </c>
       <c r="F3" t="n">
-        <v>12.14721084977219</v>
+        <v>1.973921763087981</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.69260138181415</v>
+        <v>4.337547724544799</v>
       </c>
       <c r="D4" t="n">
-        <v>13.42651450522319</v>
+        <v>2.181808607098769</v>
       </c>
       <c r="E4" t="n">
-        <v>10.07553615442021</v>
+        <v>1.637274625093284</v>
       </c>
       <c r="F4" t="n">
-        <v>12.14721084977219</v>
+        <v>1.973921763087981</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.7894961579866</v>
+        <v>7.440793125672823</v>
       </c>
       <c r="D5" t="n">
-        <v>44.73575994455499</v>
+        <v>7.269560990990185</v>
       </c>
       <c r="E5" t="n">
-        <v>10.07553615442021</v>
+        <v>1.637274625093284</v>
       </c>
       <c r="F5" t="n">
-        <v>12.14721084977219</v>
+        <v>1.973921763087981</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
